--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,95 +15,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="414">
   <si>
     <t>ناجح ✓</t>
   </si>
   <si>
-    <t>2026-02-25 15:20</t>
+    <t>2026-03-04 13:03</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>01551501457</t>
+  </si>
+  <si>
+    <t>roaaahmed21080001@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤى احمد حسين</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:37</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>01033050201</t>
+  </si>
+  <si>
+    <t>abdelfatahebrahim38@gmail.com</t>
+  </si>
+  <si>
+    <t>ابراهيم عبدالفتاح فؤاد</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:30</t>
+  </si>
+  <si>
+    <t>01501181314</t>
+  </si>
+  <si>
+    <t>bebonasser399@gamil.com</t>
+  </si>
+  <si>
+    <t>Habiba Nasser Ahmed</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:50</t>
+  </si>
+  <si>
+    <t>01069612668</t>
+  </si>
+  <si>
+    <t>meskayman999@gmail.com</t>
+  </si>
+  <si>
+    <t>مسك ايمن محمد حسن</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:58</t>
+  </si>
+  <si>
+    <t>01063365283</t>
+  </si>
+  <si>
+    <t>ehab23405@gmail.com</t>
+  </si>
+  <si>
+    <t>Adham</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-02-25 15:59</t>
   </si>
   <si>
     <t>80.0%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>01551501457</t>
-  </si>
-  <si>
-    <t>roaaahmed21080001@gmail.com</t>
-  </si>
-  <si>
-    <t>رؤى احمد حسين</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:37</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>01033050201</t>
-  </si>
-  <si>
-    <t>abdelfatahebrahim38@gmail.com</t>
-  </si>
-  <si>
-    <t>ابراهيم عبدالفتاح فؤاد</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:30</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>01501181314</t>
-  </si>
-  <si>
-    <t>bebonasser399@gamil.com</t>
-  </si>
-  <si>
-    <t>Habiba Nasser Ahmed</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:50</t>
-  </si>
-  <si>
-    <t>01069612668</t>
-  </si>
-  <si>
-    <t>meskayman999@gmail.com</t>
-  </si>
-  <si>
-    <t>مسك ايمن محمد حسن</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:58</t>
-  </si>
-  <si>
-    <t>01063365283</t>
-  </si>
-  <si>
-    <t>ehab23405@gmail.com</t>
-  </si>
-  <si>
-    <t>Adham</t>
-  </si>
-  <si>
-    <t>01094303365</t>
-  </si>
-  <si>
-    <t>Yomnamelhabrouk@gmail.com</t>
-  </si>
-  <si>
-    <t>Yomna</t>
-  </si>
-  <si>
-    <t>2026-02-25 15:59</t>
-  </si>
-  <si>
     <t>01271532097</t>
   </si>
   <si>
@@ -1142,6 +1142,66 @@
     <t>احمد محمد احمد كامل</t>
   </si>
   <si>
+    <t>2026-03-04 14:29</t>
+  </si>
+  <si>
+    <t>01156486570</t>
+  </si>
+  <si>
+    <t>ahmed1404mostafa@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد مصطفي احمد يوسف</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:55</t>
+  </si>
+  <si>
+    <t>01210081096</t>
+  </si>
+  <si>
+    <t>malaak.7assan100@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Hassan</t>
+  </si>
+  <si>
+    <t>2026-03-04 15:54</t>
+  </si>
+  <si>
+    <t>01011452702</t>
+  </si>
+  <si>
+    <t>ahmedmohamedhc2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-04 17:07</t>
+  </si>
+  <si>
+    <t>01151728245</t>
+  </si>
+  <si>
+    <t>Hshhzhxbheh@gmail.com</t>
+  </si>
+  <si>
+    <t>يوسف شريف عادل</t>
+  </si>
+  <si>
+    <t>2026-03-04 17:48</t>
+  </si>
+  <si>
+    <t>01010270581</t>
+  </si>
+  <si>
+    <t>yousefakram527@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef Akram</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -1196,7 +1256,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 14:10</t>
+    <t>تاريخ التصدير: 2026-03-04 19:30</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1644,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P98"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1607,67 +1667,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1675,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1690,32 +1750,30 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="J5" s="2">
-        <v>2</v>
-      </c>
-      <c r="K5" s="2">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>11.13</v>
+        <v>1.33</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1723,13 +1781,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1738,27 +1796,29 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>15.13</v>
+        <v>7.02</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1769,13 +1829,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1784,29 +1844,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>9.87</v>
+        <v>1.9</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1817,13 +1875,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1832,27 +1890,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>13.85</v>
+        <v>6.3</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1863,42 +1923,44 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>13.63</v>
+        <v>3.73</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1909,13 +1971,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1924,30 +1986,32 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K10" s="2">
+        <v>3</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>24.78</v>
+        <v>11.13</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1955,13 +2019,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1970,29 +2034,27 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>2.82</v>
+        <v>15.13</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -2003,19 +2065,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>8.0</v>
@@ -2024,7 +2086,7 @@
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J12" s="2">
         <v>4</v>
@@ -2037,10 +2099,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>4.4</v>
+        <v>9.87</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -2051,13 +2113,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -2066,29 +2128,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>16.23</v>
+        <v>13.85</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -2099,19 +2159,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2">
         <v>10.0</v>
@@ -2131,10 +2191,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>5.45</v>
+        <v>13.63</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -2145,13 +2205,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -2177,10 +2237,10 @@
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>7.75</v>
+        <v>24.78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -2191,13 +2251,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -2212,7 +2272,7 @@
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J16" s="2">
         <v>4</v>
@@ -2225,10 +2285,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>14.65</v>
+        <v>2.82</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -2239,42 +2299,44 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>8.05</v>
+        <v>4.4</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -2285,44 +2347,44 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>3.07</v>
+        <v>16.23</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -2333,13 +2395,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -2348,29 +2410,27 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>2.47</v>
+        <v>5.45</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -2381,13 +2441,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -2413,10 +2473,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>28.58</v>
+        <v>7.75</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -2427,13 +2487,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -2442,27 +2502,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>23.15</v>
+        <v>14.65</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -2473,13 +2535,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -2505,10 +2567,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>9.92</v>
+        <v>8.05</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -2519,47 +2581,47 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>209</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>3.85</v>
+        <v>3.07</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2567,13 +2629,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -2588,7 +2650,7 @@
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J24" s="2">
         <v>4</v>
@@ -2601,10 +2663,10 @@
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>8.83</v>
+        <v>2.47</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2615,13 +2677,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2647,10 +2709,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>6.93</v>
+        <v>28.58</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2661,13 +2723,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2693,10 +2755,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>14.12</v>
+        <v>23.15</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2707,13 +2769,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2739,10 +2801,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>8.6</v>
+        <v>9.92</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2753,47 +2815,47 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>2</v>
+        <v>209</v>
       </c>
       <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
         <v>4</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>15.27</v>
+        <v>3.85</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2801,13 +2863,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2816,27 +2878,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>13.22</v>
+        <v>8.83</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2847,13 +2911,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2862,29 +2926,27 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J30" s="2">
-        <v>4</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>5.67</v>
+        <v>6.93</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2895,44 +2957,42 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J31" s="2">
-        <v>3</v>
-      </c>
-      <c r="K31" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>6.52</v>
+        <v>14.12</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2943,13 +3003,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2958,29 +3018,27 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J32" s="2">
-        <v>4</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>11.37</v>
+        <v>8.6</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2991,42 +3049,44 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J33" s="2">
-        <v>5</v>
-      </c>
-      <c r="K33" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>14.98</v>
+        <v>15.27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -3037,13 +3097,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -3052,29 +3112,27 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J34" s="2">
-        <v>4</v>
-      </c>
-      <c r="K34" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>2.27</v>
+        <v>13.22</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -3085,13 +3143,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -3100,27 +3158,29 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J35" s="2">
-        <v>5</v>
-      </c>
-      <c r="K35" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>8.63</v>
+        <v>5.67</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -3131,42 +3191,44 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G36" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H36" s="2">
         <v>10.0</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J36" s="2">
-        <v>5</v>
-      </c>
-      <c r="K36" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2">
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>3.63</v>
+        <v>6.52</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -3177,13 +3239,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -3198,7 +3260,7 @@
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J37" s="2">
         <v>4</v>
@@ -3211,10 +3273,10 @@
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>12.13</v>
+        <v>11.37</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -3225,13 +3287,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D38" s="2">
-        <v>201118200153</v>
+        <v>261</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -3257,10 +3319,10 @@
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>3.6</v>
+        <v>14.98</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -3271,13 +3333,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -3286,27 +3348,29 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J39" s="2">
-        <v>5</v>
-      </c>
-      <c r="K39" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>5.75</v>
+        <v>2.27</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -3317,13 +3381,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -3332,29 +3396,27 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J40" s="2">
-        <v>4</v>
-      </c>
-      <c r="K40" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>13.6</v>
+        <v>8.63</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -3365,13 +3427,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -3380,29 +3442,27 @@
         <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J41" s="2">
-        <v>4</v>
-      </c>
-      <c r="K41" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>20.62</v>
+        <v>3.63</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -3413,13 +3473,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -3428,29 +3488,29 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J42" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>2.52</v>
+        <v>12.13</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -3461,13 +3521,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>221</v>
+        <v>241</v>
+      </c>
+      <c r="D43" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -3493,10 +3553,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>44.97</v>
+        <v>3.6</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -3507,13 +3567,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -3539,10 +3599,10 @@
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>21.83</v>
+        <v>5.75</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -3553,13 +3613,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -3568,27 +3628,29 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J45" s="2">
-        <v>5</v>
-      </c>
-      <c r="K45" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>13.57</v>
+        <v>13.6</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -3599,47 +3661,47 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H46" s="2">
         <v>10.0</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>209</v>
+        <v>28</v>
       </c>
       <c r="J46" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K46" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2">
         <v>5</v>
       </c>
       <c r="N46" s="2">
-        <v>0.55</v>
+        <v>20.62</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3647,13 +3709,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>3</v>
@@ -3668,7 +3730,7 @@
         <v>10.0</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J47" s="2">
         <v>3</v>
@@ -3681,10 +3743,10 @@
         <v>5</v>
       </c>
       <c r="N47" s="2">
-        <v>16.13</v>
+        <v>2.52</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>0</v>
@@ -3695,44 +3757,42 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H48" s="2">
         <v>10.0</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J48" s="2">
-        <v>3</v>
-      </c>
-      <c r="K48" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2">
         <v>5</v>
       </c>
       <c r="N48" s="2">
-        <v>4.38</v>
+        <v>44.97</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="P48" s="2" t="s">
         <v>0</v>
@@ -3743,19 +3803,19 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2">
         <v>10.0</v>
@@ -3775,10 +3835,10 @@
         <v>5</v>
       </c>
       <c r="N49" s="2">
-        <v>14.97</v>
+        <v>21.83</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="P49" s="2" t="s">
         <v>0</v>
@@ -3789,13 +3849,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>3</v>
@@ -3804,29 +3864,27 @@
         <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H50" s="2">
         <v>10.0</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J50" s="2">
-        <v>4</v>
-      </c>
-      <c r="K50" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2">
         <v>5</v>
       </c>
       <c r="N50" s="2">
-        <v>17.72</v>
+        <v>13.57</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="P50" s="2" t="s">
         <v>0</v>
@@ -3837,45 +3895,47 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="H51" s="2">
         <v>10.0</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>8</v>
+        <v>209</v>
       </c>
       <c r="J51" s="2">
-        <v>5</v>
-      </c>
-      <c r="K51" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="K51" s="2">
+        <v>4</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2">
         <v>5</v>
       </c>
       <c r="N51" s="2">
-        <v>13.77</v>
+        <v>0.55</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3883,13 +3943,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>3</v>
@@ -3898,27 +3958,29 @@
         <v>1</v>
       </c>
       <c r="G52" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H52" s="2">
         <v>10.0</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2">
-        <v>5</v>
-      </c>
-      <c r="K52" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K52" s="2">
+        <v>2</v>
+      </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2">
         <v>5</v>
       </c>
       <c r="N52" s="2">
-        <v>10.58</v>
+        <v>16.13</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>0</v>
@@ -3929,42 +3991,44 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H53" s="2">
         <v>10.0</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2">
-        <v>5</v>
-      </c>
-      <c r="K53" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K53" s="2">
+        <v>2</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2">
         <v>5</v>
       </c>
       <c r="N53" s="2">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>0</v>
@@ -3975,44 +4039,42 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H54" s="2">
         <v>10.0</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J54" s="2">
-        <v>3</v>
-      </c>
-      <c r="K54" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2">
         <v>5</v>
       </c>
       <c r="N54" s="2">
-        <v>10.4</v>
+        <v>14.97</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>0</v>
@@ -4023,13 +4085,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>3</v>
@@ -4038,27 +4100,29 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H55" s="2">
         <v>10.0</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J55" s="2">
-        <v>5</v>
-      </c>
-      <c r="K55" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2">
         <v>5</v>
       </c>
       <c r="N55" s="2">
-        <v>15.2</v>
+        <v>17.72</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>0</v>
@@ -4069,13 +4133,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>3</v>
@@ -4084,29 +4148,27 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H56" s="2">
         <v>10.0</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J56" s="2">
-        <v>4</v>
-      </c>
-      <c r="K56" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2">
         <v>5</v>
       </c>
       <c r="N56" s="2">
-        <v>6.85</v>
+        <v>13.77</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>0</v>
@@ -4117,44 +4179,42 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F57" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H57" s="2">
         <v>10.0</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J57" s="2">
-        <v>4</v>
-      </c>
-      <c r="K57" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2">
         <v>5</v>
       </c>
       <c r="N57" s="2">
-        <v>11.95</v>
+        <v>10.58</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>0</v>
@@ -4165,47 +4225,45 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H58" s="2">
         <v>10.0</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="J58" s="2">
-        <v>2</v>
-      </c>
-      <c r="K58" s="2">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2">
         <v>5</v>
       </c>
       <c r="N58" s="2">
-        <v>9.93</v>
+        <v>4.47</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4213,13 +4271,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>3</v>
@@ -4234,7 +4292,7 @@
         <v>10.0</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J59" s="2">
         <v>3</v>
@@ -4247,10 +4305,10 @@
         <v>5</v>
       </c>
       <c r="N59" s="2">
-        <v>6.2</v>
+        <v>10.4</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="P59" s="2" t="s">
         <v>0</v>
@@ -4261,13 +4319,13 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>3</v>
@@ -4293,10 +4351,10 @@
         <v>5</v>
       </c>
       <c r="N60" s="2">
-        <v>9.27</v>
+        <v>15.2</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>0</v>
@@ -4307,13 +4365,13 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>3</v>
@@ -4328,7 +4386,7 @@
         <v>10.0</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J61" s="2">
         <v>4</v>
@@ -4341,10 +4399,10 @@
         <v>5</v>
       </c>
       <c r="N61" s="2">
-        <v>4.88</v>
+        <v>6.85</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>0</v>
@@ -4355,42 +4413,44 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H62" s="2">
         <v>10.0</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J62" s="2">
-        <v>5</v>
-      </c>
-      <c r="K62" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K62" s="2">
+        <v>1</v>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2">
         <v>5</v>
       </c>
       <c r="N62" s="2">
-        <v>9.0</v>
+        <v>11.95</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>0</v>
@@ -4401,45 +4461,47 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H63" s="2">
         <v>10.0</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J63" s="2">
-        <v>5</v>
-      </c>
-      <c r="K63" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K63" s="2">
+        <v>3</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2">
         <v>5</v>
       </c>
       <c r="N63" s="2">
-        <v>4.9</v>
+        <v>9.93</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4447,13 +4509,13 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>3</v>
@@ -4462,27 +4524,29 @@
         <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H64" s="2">
         <v>10.0</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2">
-        <v>5</v>
-      </c>
-      <c r="K64" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K64" s="2">
+        <v>2</v>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2">
         <v>5</v>
       </c>
       <c r="N64" s="2">
-        <v>13.38</v>
+        <v>6.2</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>0</v>
@@ -4493,13 +4557,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>3</v>
@@ -4508,29 +4572,27 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H65" s="2">
         <v>10.0</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J65" s="2">
-        <v>3</v>
-      </c>
-      <c r="K65" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K65" s="2"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2">
         <v>5</v>
       </c>
       <c r="N65" s="2">
-        <v>17.32</v>
+        <v>9.27</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>0</v>
@@ -4541,13 +4603,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>3</v>
@@ -4562,7 +4624,7 @@
         <v>10.0</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J66" s="2">
         <v>4</v>
@@ -4575,10 +4637,10 @@
         <v>5</v>
       </c>
       <c r="N66" s="2">
-        <v>6.55</v>
+        <v>4.88</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>0</v>
@@ -4589,13 +4651,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>3</v>
@@ -4621,10 +4683,10 @@
         <v>5</v>
       </c>
       <c r="N67" s="2">
-        <v>11.38</v>
+        <v>9.0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>0</v>
@@ -4635,13 +4697,13 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>3</v>
@@ -4667,10 +4729,10 @@
         <v>5</v>
       </c>
       <c r="N68" s="2">
-        <v>15.83</v>
+        <v>4.9</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>0</v>
@@ -4681,13 +4743,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>3</v>
@@ -4696,29 +4758,27 @@
         <v>1</v>
       </c>
       <c r="G69" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H69" s="2">
         <v>10.0</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J69" s="2">
-        <v>3</v>
-      </c>
-      <c r="K69" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K69" s="2"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2">
         <v>5</v>
       </c>
       <c r="N69" s="2">
-        <v>19.23</v>
+        <v>13.38</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="P69" s="2" t="s">
         <v>0</v>
@@ -4729,13 +4789,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>3</v>
@@ -4744,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H70" s="2">
         <v>10.0</v>
@@ -4753,20 +4813,20 @@
         <v>2</v>
       </c>
       <c r="J70" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2">
         <v>5</v>
       </c>
       <c r="N70" s="2">
-        <v>10.93</v>
+        <v>17.32</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>0</v>
@@ -4777,13 +4837,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>3</v>
@@ -4792,27 +4852,29 @@
         <v>1</v>
       </c>
       <c r="G71" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H71" s="2">
         <v>10.0</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J71" s="2">
-        <v>5</v>
-      </c>
-      <c r="K71" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K71" s="2">
+        <v>1</v>
+      </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2">
         <v>5</v>
       </c>
       <c r="N71" s="2">
-        <v>14.03</v>
+        <v>6.55</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>0</v>
@@ -4823,44 +4885,42 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F72" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H72" s="2">
         <v>10.0</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J72" s="2">
-        <v>3</v>
-      </c>
-      <c r="K72" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2">
         <v>5</v>
       </c>
       <c r="N72" s="2">
-        <v>10.05</v>
+        <v>11.38</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>0</v>
@@ -4871,13 +4931,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>3</v>
@@ -4903,10 +4963,10 @@
         <v>5</v>
       </c>
       <c r="N73" s="2">
-        <v>5.58</v>
+        <v>15.83</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>0</v>
@@ -4917,19 +4977,19 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F74" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
         <v>6.0</v>
@@ -4938,7 +4998,7 @@
         <v>10.0</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2">
         <v>3</v>
@@ -4951,10 +5011,10 @@
         <v>5</v>
       </c>
       <c r="N74" s="2">
-        <v>6.3</v>
+        <v>19.23</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>0</v>
@@ -4965,13 +5025,13 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>3</v>
@@ -4980,27 +5040,29 @@
         <v>1</v>
       </c>
       <c r="G75" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H75" s="2">
         <v>10.0</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J75" s="2">
-        <v>5</v>
-      </c>
-      <c r="K75" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K75" s="2">
+        <v>1</v>
+      </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2">
         <v>5</v>
       </c>
       <c r="N75" s="2">
-        <v>20.43</v>
+        <v>10.93</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>0</v>
@@ -5011,13 +5073,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>3</v>
@@ -5026,29 +5088,27 @@
         <v>1</v>
       </c>
       <c r="G76" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H76" s="2">
         <v>10.0</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J76" s="2">
-        <v>4</v>
-      </c>
-      <c r="K76" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2">
         <v>5</v>
       </c>
       <c r="N76" s="2">
-        <v>27.58</v>
+        <v>14.03</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>0</v>
@@ -5059,42 +5119,44 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F77" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H77" s="2">
         <v>10.0</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J77" s="2">
-        <v>5</v>
-      </c>
-      <c r="K77" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K77" s="2">
+        <v>2</v>
+      </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2">
         <v>5</v>
       </c>
       <c r="N77" s="2">
-        <v>9.6</v>
+        <v>10.05</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>0</v>
@@ -5105,13 +5167,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>3</v>
@@ -5120,29 +5182,27 @@
         <v>1</v>
       </c>
       <c r="G78" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H78" s="2">
         <v>10.0</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J78" s="2">
-        <v>4</v>
-      </c>
-      <c r="K78" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2">
         <v>5</v>
       </c>
       <c r="N78" s="2">
-        <v>15.52</v>
+        <v>5.58</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>0</v>
@@ -5153,13 +5213,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>3</v>
@@ -5174,7 +5234,7 @@
         <v>10.0</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2">
         <v>3</v>
@@ -5187,10 +5247,10 @@
         <v>5</v>
       </c>
       <c r="N79" s="2">
-        <v>3.08</v>
+        <v>6.3</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>0</v>
@@ -5201,13 +5261,13 @@
         <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>3</v>
@@ -5216,29 +5276,27 @@
         <v>1</v>
       </c>
       <c r="G80" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H80" s="2">
         <v>10.0</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J80" s="2">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2">
         <v>5</v>
       </c>
       <c r="N80" s="2">
-        <v>11.55</v>
+        <v>20.43</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>0</v>
@@ -5249,13 +5307,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>3</v>
@@ -5264,27 +5322,29 @@
         <v>1</v>
       </c>
       <c r="G81" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H81" s="2">
         <v>10.0</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J81" s="2">
-        <v>5</v>
-      </c>
-      <c r="K81" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K81" s="2">
+        <v>1</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2">
         <v>5</v>
       </c>
       <c r="N81" s="2">
-        <v>11.63</v>
+        <v>27.58</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>0</v>
@@ -5295,13 +5355,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>3</v>
@@ -5327,10 +5387,10 @@
         <v>5</v>
       </c>
       <c r="N82" s="2">
-        <v>3.92</v>
+        <v>9.6</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="P82" s="2" t="s">
         <v>0</v>
@@ -5341,47 +5401,47 @@
         <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F83" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H83" s="2">
         <v>10.0</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="J83" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K83" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2">
         <v>5</v>
       </c>
       <c r="N83" s="2">
-        <v>3.42</v>
+        <v>15.52</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5389,42 +5449,44 @@
         <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H84" s="2">
         <v>10.0</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2">
-        <v>5</v>
-      </c>
-      <c r="K84" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K84" s="2">
+        <v>2</v>
+      </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2">
         <v>5</v>
       </c>
       <c r="N84" s="2">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="P84" s="2" t="s">
         <v>0</v>
@@ -5435,13 +5497,13 @@
         <v>81</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>3</v>
@@ -5450,27 +5512,29 @@
         <v>1</v>
       </c>
       <c r="G85" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H85" s="2">
         <v>10.0</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J85" s="2">
-        <v>5</v>
-      </c>
-      <c r="K85" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K85" s="2">
+        <v>2</v>
+      </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2">
         <v>5</v>
       </c>
       <c r="N85" s="2">
-        <v>10.65</v>
+        <v>11.55</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="P85" s="2" t="s">
         <v>0</v>
@@ -5481,13 +5545,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>3</v>
@@ -5513,10 +5577,10 @@
         <v>5</v>
       </c>
       <c r="N86" s="2">
-        <v>14.57</v>
+        <v>11.63</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="P86" s="2" t="s">
         <v>0</v>
@@ -5527,13 +5591,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>3</v>
@@ -5542,29 +5606,27 @@
         <v>1</v>
       </c>
       <c r="G87" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H87" s="2">
         <v>10.0</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J87" s="2">
-        <v>3</v>
-      </c>
-      <c r="K87" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K87" s="2"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2">
         <v>5</v>
       </c>
       <c r="N87" s="2">
-        <v>11.85</v>
+        <v>3.92</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P87" s="2" t="s">
         <v>0</v>
@@ -5575,45 +5637,47 @@
         <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" s="2">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="H88" s="2">
         <v>10.0</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J88" s="2">
-        <v>5</v>
-      </c>
-      <c r="K88" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="K88" s="2">
+        <v>3</v>
+      </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2">
         <v>5</v>
       </c>
       <c r="N88" s="2">
-        <v>15.85</v>
+        <v>3.42</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5621,13 +5685,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>3</v>
@@ -5653,10 +5717,10 @@
         <v>5</v>
       </c>
       <c r="N89" s="2">
-        <v>10.78</v>
+        <v>3.5</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="P89" s="2" t="s">
         <v>0</v>
@@ -5667,13 +5731,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>3</v>
@@ -5699,10 +5763,10 @@
         <v>5</v>
       </c>
       <c r="N90" s="2">
-        <v>9.37</v>
+        <v>10.65</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="P90" s="2" t="s">
         <v>0</v>
@@ -5713,19 +5777,19 @@
         <v>87</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F91" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91" s="2">
         <v>10.0</v>
@@ -5745,10 +5809,10 @@
         <v>5</v>
       </c>
       <c r="N91" s="2">
-        <v>12.77</v>
+        <v>14.57</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="P91" s="2" t="s">
         <v>0</v>
@@ -5759,13 +5823,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>3</v>
@@ -5774,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H92" s="2">
         <v>10.0</v>
@@ -5783,20 +5847,20 @@
         <v>2</v>
       </c>
       <c r="J92" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2">
         <v>5</v>
       </c>
       <c r="N92" s="2">
-        <v>9.55</v>
+        <v>11.85</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>0</v>
@@ -5807,13 +5871,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>3</v>
@@ -5839,10 +5903,10 @@
         <v>5</v>
       </c>
       <c r="N93" s="2">
-        <v>8.85</v>
+        <v>15.85</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="P93" s="2" t="s">
         <v>0</v>
@@ -5853,13 +5917,13 @@
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>3</v>
@@ -5885,10 +5949,10 @@
         <v>5</v>
       </c>
       <c r="N94" s="2">
-        <v>12.18</v>
+        <v>10.78</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>0</v>
@@ -5899,13 +5963,13 @@
         <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>3</v>
@@ -5914,29 +5978,27 @@
         <v>1</v>
       </c>
       <c r="G95" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H95" s="2">
         <v>10.0</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J95" s="2">
-        <v>3</v>
-      </c>
-      <c r="K95" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2">
         <v>5</v>
       </c>
       <c r="N95" s="2">
-        <v>17.75</v>
+        <v>9.37</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>0</v>
@@ -5947,44 +6009,42 @@
         <v>92</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H96" s="2">
         <v>10.0</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J96" s="2">
-        <v>3</v>
-      </c>
-      <c r="K96" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2">
         <v>5</v>
       </c>
       <c r="N96" s="2">
-        <v>4.1</v>
+        <v>12.77</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="P96" s="2" t="s">
         <v>0</v>
@@ -5995,13 +6055,13 @@
         <v>93</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>3</v>
@@ -6010,27 +6070,29 @@
         <v>1</v>
       </c>
       <c r="G97" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H97" s="2">
         <v>10.0</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J97" s="2">
-        <v>5</v>
-      </c>
-      <c r="K97" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K97" s="2">
+        <v>1</v>
+      </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2">
         <v>5</v>
       </c>
       <c r="N97" s="2">
-        <v>14.5</v>
+        <v>9.55</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="P97" s="2" t="s">
         <v>0</v>
@@ -6041,13 +6103,13 @@
         <v>94</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>3</v>
@@ -6056,31 +6118,265 @@
         <v>1</v>
       </c>
       <c r="G98" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H98" s="2">
         <v>10.0</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J98" s="2">
-        <v>4</v>
-      </c>
-      <c r="K98" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K98" s="2"/>
       <c r="L98" s="2"/>
       <c r="M98" s="2">
         <v>5</v>
       </c>
       <c r="N98" s="2">
-        <v>9.75</v>
+        <v>8.85</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P98" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" s="2">
+        <v>95</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H99" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J99" s="2">
+        <v>5</v>
+      </c>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2">
+        <v>5</v>
+      </c>
+      <c r="N99" s="2">
+        <v>12.18</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" s="2">
+        <v>96</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H100" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J100" s="2">
+        <v>3</v>
+      </c>
+      <c r="K100" s="2">
+        <v>2</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2">
+        <v>5</v>
+      </c>
+      <c r="N100" s="2">
+        <v>17.75</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" s="2">
+        <v>97</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H101" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J101" s="2">
+        <v>3</v>
+      </c>
+      <c r="K101" s="2">
+        <v>2</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2">
+        <v>5</v>
+      </c>
+      <c r="N101" s="2">
+        <v>4.1</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" s="2">
+        <v>98</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="2">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H102" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" s="2">
+        <v>5</v>
+      </c>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2">
+        <v>5</v>
+      </c>
+      <c r="N102" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="2">
+        <v>99</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F103" s="2">
+        <v>2</v>
+      </c>
+      <c r="G103" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H103" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J103" s="2">
+        <v>3</v>
+      </c>
+      <c r="K103" s="2">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2">
+        <v>5</v>
+      </c>
+      <c r="N103" s="2">
+        <v>9941.98</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P103" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -62,12 +62,24 @@
     <t>سهر محمد ابراهيم الرفاعي</t>
   </si>
   <si>
+    <t>2026-03-06 19:38</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>01099284562</t>
+  </si>
+  <si>
+    <t>samehsami9@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam sameh sami</t>
+  </si>
+  <si>
     <t>2026-03-06 19:28</t>
   </si>
   <si>
-    <t>80.0%</t>
-  </si>
-  <si>
     <t>01154109786</t>
   </si>
   <si>
@@ -161,7 +173,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 19:31</t>
+    <t>تاريخ التصدير: 2026-03-06 23:05</t>
   </si>
 </sst>
 </file>
@@ -549,7 +561,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -572,67 +584,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -640,13 +652,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -675,7 +687,7 @@
         <v>4.52</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -686,13 +698,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -707,7 +719,7 @@
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J6" s="2">
         <v>2</v>
@@ -723,10 +735,10 @@
         <v>2.4</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -734,13 +746,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -771,7 +783,7 @@
         <v>12.4</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -782,13 +794,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -797,27 +809,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>7.27</v>
+        <v>30.0</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -828,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -860,10 +874,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>14.32</v>
+        <v>7.27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -874,13 +888,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -906,12 +920,58 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
+        <v>14.32</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
         <v>9.72</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -173,7 +173,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 23:05</t>
+    <t>تاريخ التصدير: 2026-03-07 12:22</t>
   </si>
 </sst>
 </file>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="193">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -119,6 +119,426 @@
     <t>احمد طارق فتحي</t>
   </si>
   <si>
+    <t>2026-03-07 12:28</t>
+  </si>
+  <si>
+    <t>01095106575</t>
+  </si>
+  <si>
+    <t>hanawalynono@gmail.com</t>
+  </si>
+  <si>
+    <t>هنا والي صالح</t>
+  </si>
+  <si>
+    <t>2026-03-07 22:34</t>
+  </si>
+  <si>
+    <t>01020745750</t>
+  </si>
+  <si>
+    <t>farragyassin4@gmail.com</t>
+  </si>
+  <si>
+    <t>Yassin Farrag</t>
+  </si>
+  <si>
+    <t>2026-03-10 17:47</t>
+  </si>
+  <si>
+    <t>01226990421</t>
+  </si>
+  <si>
+    <t>Hussienahmedmounir@gmail.com</t>
+  </si>
+  <si>
+    <t>حسين احمد منير</t>
+  </si>
+  <si>
+    <t>2026-03-10 21:32</t>
+  </si>
+  <si>
+    <t>01012965454</t>
+  </si>
+  <si>
+    <t>hyawalid788@gmail.com</t>
+  </si>
+  <si>
+    <t>hya walid helal</t>
+  </si>
+  <si>
+    <t>2026-03-10 22:41</t>
+  </si>
+  <si>
+    <t>01010003985</t>
+  </si>
+  <si>
+    <t>mahmoudxhj@GMAIL.cOM</t>
+  </si>
+  <si>
+    <t>محمود محمد ضياء الدين محمود</t>
+  </si>
+  <si>
+    <t>2026-03-11 02:42</t>
+  </si>
+  <si>
+    <t>01061920915</t>
+  </si>
+  <si>
+    <t>goudysherif@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد شريف</t>
+  </si>
+  <si>
+    <t>2026-03-11 19:01</t>
+  </si>
+  <si>
+    <t>01228047462</t>
+  </si>
+  <si>
+    <t>Yousefsonic22@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef hesham</t>
+  </si>
+  <si>
+    <t>2026-03-11 03:51</t>
+  </si>
+  <si>
+    <t>01149060505</t>
+  </si>
+  <si>
+    <t>yasminmahmoud3032010@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسمين محمود محمد خلاف</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:07</t>
+  </si>
+  <si>
+    <t>01006392755</t>
+  </si>
+  <si>
+    <t>ezz44013@gmail.com</t>
+  </si>
+  <si>
+    <t>عز الدين أيمن</t>
+  </si>
+  <si>
+    <t>2026-03-11 12:32</t>
+  </si>
+  <si>
+    <t>01063365283</t>
+  </si>
+  <si>
+    <t>ehab23405@gmail.com</t>
+  </si>
+  <si>
+    <t>Adham</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:20</t>
+  </si>
+  <si>
+    <t>01117015370</t>
+  </si>
+  <si>
+    <t>salmayasserlolo7@gmail.com</t>
+  </si>
+  <si>
+    <t>سلمى ياسر احمد</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:29</t>
+  </si>
+  <si>
+    <t>01271532097</t>
+  </si>
+  <si>
+    <t>marlygmghobrial@gmail.com</t>
+  </si>
+  <si>
+    <t>مارلي جورج موريس</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:48</t>
+  </si>
+  <si>
+    <t>01124926013</t>
+  </si>
+  <si>
+    <t>marwanelnakeeb2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Marwan omar</t>
+  </si>
+  <si>
+    <t>2026-03-11 13:57</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>01501045643</t>
+  </si>
+  <si>
+    <t>elawadyahmed999@gmial.com</t>
+  </si>
+  <si>
+    <t>Elawady Ahmed elawady</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:24</t>
+  </si>
+  <si>
+    <t>01283830831</t>
+  </si>
+  <si>
+    <t>4000ahmedwael@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد وائل صلاح</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:26</t>
+  </si>
+  <si>
+    <t>01011452702</t>
+  </si>
+  <si>
+    <t>ahmedmohamedhc2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Ahmed Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-11 15:54</t>
+  </si>
+  <si>
+    <t>01007991680</t>
+  </si>
+  <si>
+    <t>nada.gamal196@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>2026-03-11 16:15</t>
+  </si>
+  <si>
+    <t>01069526879</t>
+  </si>
+  <si>
+    <t>Safawael31@gmail.com</t>
+  </si>
+  <si>
+    <t>Safa wael fathy</t>
+  </si>
+  <si>
+    <t>2026-03-11 16:52</t>
+  </si>
+  <si>
+    <t>01113365191</t>
+  </si>
+  <si>
+    <t>faridamahmoud13579@gmail.com</t>
+  </si>
+  <si>
+    <t>فريدة محمود عبدالحسيب احمد</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:09</t>
+  </si>
+  <si>
+    <t>01026535018</t>
+  </si>
+  <si>
+    <t>Janaeslam1919@gmail.com</t>
+  </si>
+  <si>
+    <t>جنى إسلام غريب</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:06</t>
+  </si>
+  <si>
+    <t>01060463907</t>
+  </si>
+  <si>
+    <t>Mernarefaat2345@gmail.com</t>
+  </si>
+  <si>
+    <t>Merna refaat Mahmoud</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:13</t>
+  </si>
+  <si>
+    <t>01098576784</t>
+  </si>
+  <si>
+    <t>samakhaled6665@gmail.com</t>
+  </si>
+  <si>
+    <t>Sama Khaled</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:10</t>
+  </si>
+  <si>
+    <t>01022023062</t>
+  </si>
+  <si>
+    <t>malakmohammedalaa94@gmail.com</t>
+  </si>
+  <si>
+    <t>ملك محمد علاء الدين</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:07</t>
+  </si>
+  <si>
+    <t>01010103820</t>
+  </si>
+  <si>
+    <t>somiasami88@gmail.com</t>
+  </si>
+  <si>
+    <t>salma mohamed mahmoud</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:17</t>
+  </si>
+  <si>
+    <t>01156486570</t>
+  </si>
+  <si>
+    <t>ahmed1404mostafa@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد مصطفي احمد يوسف</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:37</t>
+  </si>
+  <si>
+    <t>01010270581</t>
+  </si>
+  <si>
+    <t>yousefakram527@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef Akram</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:46</t>
+  </si>
+  <si>
+    <t>01097794201</t>
+  </si>
+  <si>
+    <t>aytensaleh6@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayten Saleh Mostafa</t>
+  </si>
+  <si>
+    <t>2026-03-11 17:55</t>
+  </si>
+  <si>
+    <t>01023876919</t>
+  </si>
+  <si>
+    <t>yassinahmedsaid139@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين احمد سعيد</t>
+  </si>
+  <si>
+    <t>2026-03-11 18:00</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-03-11 18:39</t>
+  </si>
+  <si>
+    <t>01012424377</t>
+  </si>
+  <si>
+    <t>janayousry@2008gmail.com</t>
+  </si>
+  <si>
+    <t>jana ahmed mohmed yousry</t>
+  </si>
+  <si>
+    <t>2026-03-11 18:44</t>
+  </si>
+  <si>
+    <t>01111427742</t>
+  </si>
+  <si>
+    <t>maryam.hossamudin@gmail.com</t>
+  </si>
+  <si>
+    <t>maryam</t>
+  </si>
+  <si>
+    <t>2026-03-11 18:42</t>
+  </si>
+  <si>
+    <t>01110668723</t>
+  </si>
+  <si>
+    <t>abdoeidbody2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Abdullah Eid saber</t>
+  </si>
+  <si>
+    <t>2026-03-11 18:56</t>
+  </si>
+  <si>
+    <t>01157331074</t>
+  </si>
+  <si>
+    <t>farahgadallh@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah Ahmed mohamed</t>
+  </si>
+  <si>
+    <t>01100682703</t>
+  </si>
+  <si>
+    <t>Lara.eldiasti@gmail.com</t>
+  </si>
+  <si>
+    <t>لارا الحسن الديسطي</t>
+  </si>
+  <si>
+    <t>2026-03-11 19:00</t>
+  </si>
+  <si>
+    <t>01014956583</t>
+  </si>
+  <si>
+    <t>mennaebrahim543@gmail.com</t>
+  </si>
+  <si>
+    <t>Menna Ibrahim</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -173,7 +593,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-07 12:22</t>
+    <t>تاريخ التصدير: 2026-03-11 19:09</t>
   </si>
 </sst>
 </file>
@@ -561,7 +981,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -584,67 +1004,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -652,13 +1072,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -684,10 +1104,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4.52</v>
+        <v>3.57</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -698,47 +1118,47 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J6" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>2.4</v>
+        <v>6.35</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -746,13 +1166,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -761,29 +1181,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>12.4</v>
+        <v>8.53</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -794,13 +1212,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -809,29 +1227,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>30.0</v>
+        <v>4.12</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -842,13 +1260,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -857,27 +1275,29 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J9" s="2">
-        <v>5</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>7.27</v>
+        <v>7.55</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -888,13 +1308,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -903,27 +1323,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>14.32</v>
+        <v>6.75</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>7</v>
+        <v>151</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -934,13 +1356,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>4</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -966,12 +1388,1654 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
+        <v>11.95</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>8.58</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>8.48</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="2">
+        <v>4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="2">
+        <v>3</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2">
+        <v>2.53</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2">
+        <v>2.35</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2">
+        <v>5</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5.67</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2">
+        <v>5</v>
+      </c>
+      <c r="N18" s="2">
+        <v>9.97</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>5</v>
+      </c>
+      <c r="N19" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2">
+        <v>5</v>
+      </c>
+      <c r="N20" s="2">
+        <v>9.63</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2">
+        <v>5</v>
+      </c>
+      <c r="N21" s="2">
+        <v>13.05</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="2">
+        <v>4</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>15.22</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J24" s="2">
+        <v>3</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>1.18</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2">
+        <v>5</v>
+      </c>
+      <c r="N25" s="2">
+        <v>24.53</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J26" s="2">
+        <v>3</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1.28</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2">
+        <v>5</v>
+      </c>
+      <c r="N27" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="2">
+        <v>4</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
+        <v>5</v>
+      </c>
+      <c r="N28" s="2">
+        <v>3.32</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
+        <v>5</v>
+      </c>
+      <c r="N29" s="2">
+        <v>13.52</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="2">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
+        <v>5</v>
+      </c>
+      <c r="N30" s="2">
+        <v>4.75</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="2">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
+        <v>5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>2.85</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="2">
+        <v>4</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>5</v>
+      </c>
+      <c r="N32" s="2">
+        <v>13.73</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="2">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>925.05</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="2">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J34" s="2">
+        <v>5</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2">
+        <v>5</v>
+      </c>
+      <c r="N34" s="2">
+        <v>6.43</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="2">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="2">
+        <v>4</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2">
+        <v>5</v>
+      </c>
+      <c r="N35" s="2">
+        <v>4.63</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>5</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2">
+        <v>5</v>
+      </c>
+      <c r="N36" s="2">
+        <v>14.02</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="2">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J37" s="2">
+        <v>5</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2">
+        <v>5</v>
+      </c>
+      <c r="N37" s="2">
+        <v>2.45</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="2">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="2">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
+        <v>3.03</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="2">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="2">
+        <v>4</v>
+      </c>
+      <c r="K39" s="2">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2">
+        <v>5</v>
+      </c>
+      <c r="N39" s="2">
+        <v>11.05</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J40" s="2">
+        <v>5</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2">
+        <v>5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>4.52</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="2">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" s="2">
+        <v>2</v>
+      </c>
+      <c r="K41" s="2">
+        <v>3</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2">
+        <v>5</v>
+      </c>
+      <c r="N41" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="2">
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="2">
+        <v>4</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2">
+        <v>5</v>
+      </c>
+      <c r="N42" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="2">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="2">
+        <v>4</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2">
+        <v>5</v>
+      </c>
+      <c r="N43" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="2">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>5</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2">
+        <v>5</v>
+      </c>
+      <c r="N44" s="2">
+        <v>7.27</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J45" s="2">
+        <v>5</v>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2">
+        <v>5</v>
+      </c>
+      <c r="N45" s="2">
+        <v>14.32</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2">
+        <v>42</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J46" s="2">
+        <v>5</v>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2">
+        <v>5</v>
+      </c>
+      <c r="N46" s="2">
         <v>9.72</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="s">
+      <c r="O46" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P46" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="200">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -539,6 +539,27 @@
     <t>Menna Ibrahim</t>
   </si>
   <si>
+    <t>2026-03-11 19:10</t>
+  </si>
+  <si>
+    <t>01026933947</t>
+  </si>
+  <si>
+    <t>malaksamykamel2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Samy</t>
+  </si>
+  <si>
+    <t>2026-03-11 19:23</t>
+  </si>
+  <si>
+    <t>karimmowafak@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim Mowafak</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -593,7 +614,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 19:09</t>
+    <t>تاريخ التصدير: 2026-03-11 20:14</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1002,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1004,67 +1025,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1072,13 +1093,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
+      </c>
+      <c r="D5" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1087,27 +1108,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>3.57</v>
+        <v>1.52</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1118,13 +1141,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1133,29 +1156,27 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>6.35</v>
+        <v>5.43</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>58</v>
+        <v>174</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1166,13 +1187,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1198,10 +1219,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>8.53</v>
+        <v>3.57</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1212,13 +1233,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1227,29 +1248,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>4.12</v>
+        <v>6.35</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1260,13 +1281,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1275,29 +1296,27 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>7.55</v>
+        <v>8.53</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1308,13 +1327,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1323,29 +1342,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>6.75</v>
+        <v>4.12</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1356,13 +1375,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1371,27 +1390,29 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>11.95</v>
+        <v>7.55</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1402,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1436,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>8.58</v>
+        <v>6.75</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1450,13 +1471,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1482,10 +1503,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>8.48</v>
+        <v>11.95</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1496,13 +1517,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1530,10 +1551,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>1.75</v>
+        <v>8.58</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1544,13 +1565,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1559,29 +1580,27 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H15" s="2">
         <v>10.0</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="J15" s="2">
-        <v>3</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2">
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>2.53</v>
+        <v>8.48</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1592,13 +1611,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1607,27 +1626,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1638,13 +1659,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1653,27 +1674,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="K17" s="2">
         <v>2</v>
       </c>
-      <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>5.67</v>
+        <v>2.53</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1684,13 +1707,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1699,29 +1722,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>9.97</v>
+        <v>2.35</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1732,13 +1753,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1747,29 +1768,27 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1780,13 +1799,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1795,27 +1814,29 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>9.63</v>
+        <v>9.97</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1826,13 +1847,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1841,27 +1862,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>13.05</v>
+        <v>5.8</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1872,13 +1895,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1887,29 +1910,27 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>15.22</v>
+        <v>9.63</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1920,13 +1941,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -1952,10 +1973,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>14.6</v>
+        <v>13.05</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1966,13 +1987,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -1981,29 +2002,29 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>1.18</v>
+        <v>15.22</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -2014,13 +2035,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -2046,10 +2067,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>24.53</v>
+        <v>14.6</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2060,13 +2081,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2094,10 +2115,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2108,13 +2129,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2140,10 +2161,10 @@
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>8.6</v>
+        <v>24.53</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2154,13 +2175,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2169,29 +2190,29 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="J28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>3.32</v>
+        <v>1.28</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2202,13 +2223,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2234,10 +2255,10 @@
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>13.52</v>
+        <v>8.6</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2248,13 +2269,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2263,27 +2284,29 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H30" s="2">
         <v>10.0</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J30" s="2">
-        <v>5</v>
-      </c>
-      <c r="K30" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>4.75</v>
+        <v>3.32</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2294,13 +2317,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2326,10 +2349,10 @@
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>2.85</v>
+        <v>13.52</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2340,13 +2363,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2355,29 +2378,27 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H32" s="2">
         <v>10.0</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2">
-        <v>4</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2">
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>13.73</v>
+        <v>4.75</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2388,19 +2409,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2">
         <v>10.0</v>
@@ -2420,10 +2441,10 @@
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>925.05</v>
+        <v>2.85</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2434,13 +2455,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2449,27 +2470,29 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J34" s="2">
-        <v>5</v>
-      </c>
-      <c r="K34" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>6.43</v>
+        <v>13.73</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2480,44 +2503,42 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H35" s="2">
         <v>10.0</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2">
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>4.63</v>
+        <v>925.05</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2528,13 +2549,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2560,10 +2581,10 @@
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>14.02</v>
+        <v>6.43</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2574,13 +2595,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2589,27 +2610,29 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J37" s="2">
-        <v>5</v>
-      </c>
-      <c r="K37" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>2.45</v>
+        <v>4.63</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2620,44 +2643,42 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H38" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="J38" s="2">
-        <v>4</v>
-      </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>3.03</v>
+        <v>14.02</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -2668,13 +2689,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2683,29 +2704,27 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H39" s="2">
         <v>10.0</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J39" s="2">
-        <v>4</v>
-      </c>
-      <c r="K39" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2">
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>11.05</v>
+        <v>2.45</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2716,42 +2735,44 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H40" s="2">
         <v>10.0</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J40" s="2">
-        <v>5</v>
-      </c>
-      <c r="K40" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2">
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>4.52</v>
+        <v>3.03</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -2762,47 +2783,47 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="2">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H41" s="2">
         <v>10.0</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2">
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>2.4</v>
+        <v>11.05</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -2810,13 +2831,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -2825,29 +2846,27 @@
         <v>1</v>
       </c>
       <c r="G42" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H42" s="2">
         <v>10.0</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2">
-        <v>4</v>
-      </c>
-      <c r="K42" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2">
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>12.4</v>
+        <v>4.52</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -2858,47 +2877,47 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="H43" s="2">
         <v>10.0</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J43" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K43" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2">
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>30.0</v>
+        <v>2.4</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -2906,13 +2925,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -2921,27 +2940,29 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J44" s="2">
-        <v>5</v>
-      </c>
-      <c r="K44" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
-        <v>7.27</v>
+        <v>12.4</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>0</v>
@@ -2952,13 +2973,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>3</v>
@@ -2967,27 +2988,29 @@
         <v>1</v>
       </c>
       <c r="G45" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H45" s="2">
         <v>10.0</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J45" s="2">
-        <v>5</v>
-      </c>
-      <c r="K45" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K45" s="2">
+        <v>1</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2">
         <v>5</v>
       </c>
       <c r="N45" s="2">
-        <v>14.32</v>
+        <v>30.0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="P45" s="2" t="s">
         <v>0</v>
@@ -2998,13 +3021,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>3</v>
@@ -3030,12 +3053,104 @@
         <v>5</v>
       </c>
       <c r="N46" s="2">
+        <v>7.27</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="2">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2">
+        <v>5</v>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2">
+        <v>5</v>
+      </c>
+      <c r="N47" s="2">
+        <v>14.32</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="2">
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48" s="2">
+        <v>5</v>
+      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2">
+        <v>5</v>
+      </c>
+      <c r="N48" s="2">
         <v>9.72</v>
       </c>
-      <c r="O46" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P46" s="2" t="s">
+      <c r="O48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="183">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -233,6 +233,282 @@
     <t>احمد سامح حسين</t>
   </si>
   <si>
+    <t>2026-03-13 19:32</t>
+  </si>
+  <si>
+    <t>01121970064</t>
+  </si>
+  <si>
+    <t>Ahmedmakg7@gmail.com</t>
+  </si>
+  <si>
+    <t>احمد محمد احمد كامل</t>
+  </si>
+  <si>
+    <t>2026-03-16 14:46</t>
+  </si>
+  <si>
+    <t>01125776411</t>
+  </si>
+  <si>
+    <t>radwanosama414@gmail.com</t>
+  </si>
+  <si>
+    <t>Radwan Osama</t>
+  </si>
+  <si>
+    <t>2026-03-18 00:22</t>
+  </si>
+  <si>
+    <t>01117015370</t>
+  </si>
+  <si>
+    <t>salmayasserlolo7@gmail.com</t>
+  </si>
+  <si>
+    <t>سلمى ياسر احمد</t>
+  </si>
+  <si>
+    <t>2026-03-18 02:51</t>
+  </si>
+  <si>
+    <t>01100682703</t>
+  </si>
+  <si>
+    <t>Lara.eldiasti@gmail.com</t>
+  </si>
+  <si>
+    <t>لارا الحسن الديسطي</t>
+  </si>
+  <si>
+    <t>2026-03-18 03:31</t>
+  </si>
+  <si>
+    <t>01149060505</t>
+  </si>
+  <si>
+    <t>yasminmahmoud3032010@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسمين محمود محمد خلاف</t>
+  </si>
+  <si>
+    <t>2026-03-18 07:30</t>
+  </si>
+  <si>
+    <t>01100422373</t>
+  </si>
+  <si>
+    <t>menna262menna@gmail.com</t>
+  </si>
+  <si>
+    <t>منه مختار عبد القادر</t>
+  </si>
+  <si>
+    <t>2026-03-18 12:41</t>
+  </si>
+  <si>
+    <t>01012965454</t>
+  </si>
+  <si>
+    <t>hyawalid788@gmail.com</t>
+  </si>
+  <si>
+    <t>hya walid helal</t>
+  </si>
+  <si>
+    <t>2026-03-18 13:53</t>
+  </si>
+  <si>
+    <t>01113365191</t>
+  </si>
+  <si>
+    <t>faridamahmoud13579@gmail.com</t>
+  </si>
+  <si>
+    <t>فريدة محمود عبدالحسيب احمد</t>
+  </si>
+  <si>
+    <t>2026-03-18 13:45</t>
+  </si>
+  <si>
+    <t>01092255761</t>
+  </si>
+  <si>
+    <t>habibagalal552004@gmail.com</t>
+  </si>
+  <si>
+    <t>moustafa galal</t>
+  </si>
+  <si>
+    <t>2026-03-18 14:13</t>
+  </si>
+  <si>
+    <t>01276678983</t>
+  </si>
+  <si>
+    <t>mm8028203@gmail.com</t>
+  </si>
+  <si>
+    <t>مؤمن محمد مصطفي عبدالسلام</t>
+  </si>
+  <si>
+    <t>2026-03-18 15:37</t>
+  </si>
+  <si>
+    <t>01501045643</t>
+  </si>
+  <si>
+    <t>elawadyahmed999@gmial.com</t>
+  </si>
+  <si>
+    <t>Elawady Ahmed elawady</t>
+  </si>
+  <si>
+    <t>2026-03-18 15:51</t>
+  </si>
+  <si>
+    <t>01014956583</t>
+  </si>
+  <si>
+    <t>mennaebrahim543@gmail.com</t>
+  </si>
+  <si>
+    <t>Menna Ibrahim</t>
+  </si>
+  <si>
+    <t>2026-03-18 16:06</t>
+  </si>
+  <si>
+    <t>01228047462</t>
+  </si>
+  <si>
+    <t>Yousefsonic22@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef hesham</t>
+  </si>
+  <si>
+    <t>2026-03-18 16:43</t>
+  </si>
+  <si>
+    <t>01225460949</t>
+  </si>
+  <si>
+    <t>hm3947263@gmail.com</t>
+  </si>
+  <si>
+    <t>Rahma mohamed mostafa</t>
+  </si>
+  <si>
+    <t>2026-03-18 17:07</t>
+  </si>
+  <si>
+    <t>01094303365</t>
+  </si>
+  <si>
+    <t>Yomnamelhabrouk@gmail.com</t>
+  </si>
+  <si>
+    <t>Yomna</t>
+  </si>
+  <si>
+    <t>2026-03-18 17:36</t>
+  </si>
+  <si>
+    <t>01023876919</t>
+  </si>
+  <si>
+    <t>yassinahmedsaid139@gmail.com</t>
+  </si>
+  <si>
+    <t>ياسين احمد سعيد</t>
+  </si>
+  <si>
+    <t>2026-03-18 17:30</t>
+  </si>
+  <si>
+    <t>01010270581</t>
+  </si>
+  <si>
+    <t>yousefakram527@gmail.com</t>
+  </si>
+  <si>
+    <t>Yousef Akram</t>
+  </si>
+  <si>
+    <t>2026-03-18 17:37</t>
+  </si>
+  <si>
+    <t>01124926013</t>
+  </si>
+  <si>
+    <t>marwanelnakeeb2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Marwan omar</t>
+  </si>
+  <si>
+    <t>2026-03-18 17:51</t>
+  </si>
+  <si>
+    <t>01022023062</t>
+  </si>
+  <si>
+    <t>malakmohammedalaa94@gmail.com</t>
+  </si>
+  <si>
+    <t>ملك محمد علاء الدين</t>
+  </si>
+  <si>
+    <t>2026-03-18 18:15</t>
+  </si>
+  <si>
+    <t>01065596920</t>
+  </si>
+  <si>
+    <t>caramella3750@gmail.com</t>
+  </si>
+  <si>
+    <t>Carma Ehab</t>
+  </si>
+  <si>
+    <t>2026-03-18 19:04</t>
+  </si>
+  <si>
+    <t>01012424377</t>
+  </si>
+  <si>
+    <t>janayousry@2008gmail.com</t>
+  </si>
+  <si>
+    <t>jana ahmed mohmed yousry</t>
+  </si>
+  <si>
+    <t>2026-03-18 19:13</t>
+  </si>
+  <si>
+    <t>01283830831</t>
+  </si>
+  <si>
+    <t>4000ahmedwael@gmail.com</t>
+  </si>
+  <si>
+    <t>أحمد وائل صلاح</t>
+  </si>
+  <si>
+    <t>2026-03-18 19:17</t>
+  </si>
+  <si>
+    <t>01157331074</t>
+  </si>
+  <si>
+    <t>farahgadallh@gmail.com</t>
+  </si>
+  <si>
+    <t>Farah Ahmed mohamed</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -287,7 +563,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-13 19:30</t>
+    <t>تاريخ التصدير: 2026-03-18 19:25</t>
   </si>
 </sst>
 </file>
@@ -675,7 +951,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -698,67 +974,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>72</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -766,13 +1042,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -798,10 +1074,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>6.48</v>
+        <v>9.68</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -812,13 +1088,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -844,10 +1120,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>8.63</v>
+        <v>12.75</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -858,13 +1134,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -890,10 +1166,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>13.15</v>
+        <v>23.3</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -904,13 +1180,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -936,10 +1212,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>4.72</v>
+        <v>4.78</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -950,13 +1226,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -982,10 +1258,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>8.92</v>
+        <v>5.43</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -996,13 +1272,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1011,29 +1287,27 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>3.68</v>
+        <v>6.92</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1044,13 +1318,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1059,29 +1333,27 @@
         <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>9.55</v>
+        <v>1.55</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1092,13 +1364,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1124,10 +1396,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>2.0</v>
+        <v>11.22</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1138,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>129</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1170,10 +1442,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>9.67</v>
+        <v>8.62</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1184,13 +1456,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1216,10 +1488,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>4.23</v>
+        <v>7.13</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1230,13 +1502,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1262,10 +1534,10 @@
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>5.92</v>
+        <v>3.43</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1276,13 +1548,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1308,10 +1580,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>7.37</v>
+        <v>4.52</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1322,13 +1594,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1354,10 +1626,10 @@
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>4.85</v>
+        <v>4.28</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1368,13 +1640,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1400,10 +1672,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>20.37</v>
+        <v>2.98</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1414,13 +1686,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1446,10 +1718,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>6.92</v>
+        <v>3.68</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1460,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1492,10 +1764,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>5.18</v>
+        <v>14.02</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1506,13 +1778,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1521,31 +1793,1095 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H21" s="2">
         <v>10.0</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2">
         <v>5</v>
       </c>
       <c r="N21" s="2">
+        <v>14.13</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>12.43</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5</v>
+      </c>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2">
+        <v>7.68</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2">
+        <v>5</v>
+      </c>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>11.97</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2">
+        <v>5</v>
+      </c>
+      <c r="N25" s="2">
+        <v>14.43</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>4</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2">
+        <v>5</v>
+      </c>
+      <c r="N27" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2">
+        <v>5</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
+        <v>5</v>
+      </c>
+      <c r="N28" s="2">
+        <v>6.48</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
+        <v>5</v>
+      </c>
+      <c r="N29" s="2">
+        <v>8.63</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="2">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
+        <v>5</v>
+      </c>
+      <c r="N30" s="2">
+        <v>13.15</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="2">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
+        <v>5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>4.72</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="2">
+        <v>5</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>5</v>
+      </c>
+      <c r="N32" s="2">
+        <v>8.92</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="2">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>4</v>
+      </c>
+      <c r="K33" s="2">
+        <v>1</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2">
+        <v>5</v>
+      </c>
+      <c r="N33" s="2">
+        <v>3.68</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="2">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2">
+        <v>5</v>
+      </c>
+      <c r="N34" s="2">
+        <v>9.55</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="2">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="2">
+        <v>5</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2">
+        <v>5</v>
+      </c>
+      <c r="N35" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2">
+        <v>32</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="2">
+        <v>5</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2">
+        <v>5</v>
+      </c>
+      <c r="N36" s="2">
+        <v>9.67</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="2">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="2">
+        <v>5</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2">
+        <v>5</v>
+      </c>
+      <c r="N37" s="2">
+        <v>4.23</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="2">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" s="2">
+        <v>5</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2">
+        <v>5</v>
+      </c>
+      <c r="N38" s="2">
+        <v>5.92</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="2">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" s="2">
+        <v>5</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2">
+        <v>5</v>
+      </c>
+      <c r="N39" s="2">
+        <v>7.37</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="2">
+        <v>36</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" s="2">
+        <v>5</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2">
+        <v>5</v>
+      </c>
+      <c r="N40" s="2">
+        <v>4.85</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="2">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="2">
+        <v>5</v>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2">
+        <v>5</v>
+      </c>
+      <c r="N41" s="2">
+        <v>20.37</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="2">
+        <v>38</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="2">
+        <v>5</v>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2">
+        <v>5</v>
+      </c>
+      <c r="N42" s="2">
+        <v>6.92</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="2">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="2">
+        <v>5</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2">
+        <v>5</v>
+      </c>
+      <c r="N43" s="2">
+        <v>5.18</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="2">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>4</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2">
+        <v>5</v>
+      </c>
+      <c r="N44" s="2">
         <v>24.78</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P21" s="2" t="s">
+      <c r="O44" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P44" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -563,7 +563,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 19:25</t>
+    <t>تاريخ التصدير: 2026-03-18 20:39</t>
   </si>
 </sst>
 </file>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -563,7 +563,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 20:39</t>
+    <t>تاريخ التصدير: 2026-03-18 21:18</t>
   </si>
 </sst>
 </file>

--- a/2sci_center.xlsx
+++ b/2sci_center.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="199">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -509,6 +509,54 @@
     <t>Farah Ahmed mohamed</t>
   </si>
   <si>
+    <t>2026-03-25 15:01</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>karimmowafak@gmail.com</t>
+  </si>
+  <si>
+    <t>Karim Mowafak</t>
+  </si>
+  <si>
+    <t>2026-03-26 04:44</t>
+  </si>
+  <si>
+    <t>01120961209</t>
+  </si>
+  <si>
+    <t>masa1412009@gmail.com</t>
+  </si>
+  <si>
+    <t>Masa mohamed mohy</t>
+  </si>
+  <si>
+    <t>2026-04-02 16:51</t>
+  </si>
+  <si>
+    <t>01030133382</t>
+  </si>
+  <si>
+    <t>hamza2210mg@gmail.com</t>
+  </si>
+  <si>
+    <t>Hamza</t>
+  </si>
+  <si>
+    <t>2026-04-03 06:32</t>
+  </si>
+  <si>
+    <t>01555066805</t>
+  </si>
+  <si>
+    <t>mohammed.el.shazly2009@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد أسامة محمد الشاذلي</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -563,7 +611,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-18 21:18</t>
+    <t>تاريخ التصدير: 2026-04-03 16:45</t>
   </si>
 </sst>
 </file>
@@ -951,7 +999,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -974,67 +1022,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1042,13 +1090,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -1074,10 +1122,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>9.68</v>
+        <v>3.6</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -1088,13 +1136,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -1120,10 +1168,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>12.75</v>
+        <v>3.58</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -1134,13 +1182,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -1166,10 +1214,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>23.3</v>
+        <v>9.7</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1180,13 +1228,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
+      </c>
+      <c r="D8" s="2">
+        <v>201118200153</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -1195,27 +1243,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>8</v>
+        <v>165</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>4.78</v>
+        <v>1.38</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1226,13 +1276,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1258,10 +1308,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>5.43</v>
+        <v>9.68</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1272,13 +1322,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1304,10 +1354,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>6.92</v>
+        <v>12.75</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1318,13 +1368,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1350,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>1.55</v>
+        <v>23.3</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1364,13 +1414,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1396,10 +1446,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>11.22</v>
+        <v>4.78</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1410,13 +1460,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1442,10 +1492,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>8.62</v>
+        <v>5.43</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1456,13 +1506,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1488,10 +1538,10 @@
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>7.13</v>
+        <v>6.92</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1502,13 +1552,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1534,10 +1584,10 @@
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>3.43</v>
+        <v>1.55</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1548,13 +1598,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1580,10 +1630,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>4.52</v>
+        <v>11.22</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1594,13 +1644,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1626,10 +1676,10 @@
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>4.28</v>
+        <v>8.62</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1640,13 +1690,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1672,10 +1722,10 @@
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>2.98</v>
+        <v>7.13</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1686,13 +1736,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1718,10 +1768,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>3.68</v>
+        <v>3.43</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1732,13 +1782,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1764,10 +1814,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>14.02</v>
+        <v>4.52</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1778,13 +1828,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1810,10 +1860,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>14.13</v>
+        <v>4.28</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1824,13 +1874,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1856,10 +1906,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>12.43</v>
+        <v>2.98</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1870,13 +1920,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
@@ -1902,10 +1952,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>7.68</v>
+        <v>3.68</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1916,13 +1966,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -1948,10 +1998,10 @@
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>11.97</v>
+        <v>14.02</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -1962,13 +2012,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -1994,10 +2044,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>14.43</v>
+        <v>14.13</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -2008,13 +2058,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -2040,10 +2090,10 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>2.7</v>
+        <v>12.43</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -2054,13 +2104,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
@@ -2069,29 +2119,27 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>11.8</v>
+        <v>7.68</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -2102,13 +2150,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
@@ -2134,10 +2182,10 @@
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>6.48</v>
+        <v>11.97</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2148,13 +2196,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2180,10 +2228,10 @@
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>8.63</v>
+        <v>14.43</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2194,13 +2242,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>3</v>
@@ -2226,10 +2274,10 @@
         <v>5</v>
       </c>
       <c r="N30" s="2">
-        <v>13.15</v>
+        <v>2.7</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>0</v>
@@ -2240,13 +2288,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>3</v>
@@ -2255,27 +2303,29 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H31" s="2">
         <v>10.0</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2">
-        <v>5</v>
-      </c>
-      <c r="K31" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2">
         <v>5</v>
       </c>
       <c r="N31" s="2">
-        <v>4.72</v>
+        <v>11.8</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>0</v>
@@ -2286,13 +2336,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>3</v>
@@ -2318,10 +2368,10 @@
         <v>5</v>
       </c>
       <c r="N32" s="2">
-        <v>8.92</v>
+        <v>6.48</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>0</v>
@@ -2332,13 +2382,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>3</v>
@@ -2347,29 +2397,27 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H33" s="2">
         <v>10.0</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J33" s="2">
-        <v>4</v>
-      </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2">
         <v>5</v>
       </c>
       <c r="N33" s="2">
-        <v>3.68</v>
+        <v>8.63</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P33" s="2" t="s">
         <v>0</v>
@@ -2380,13 +2428,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>3</v>
@@ -2395,29 +2443,27 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H34" s="2">
         <v>10.0</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J34" s="2">
-        <v>4</v>
-      </c>
-      <c r="K34" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2">
         <v>5</v>
       </c>
       <c r="N34" s="2">
-        <v>9.55</v>
+        <v>13.15</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="P34" s="2" t="s">
         <v>0</v>
@@ -2428,13 +2474,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>3</v>
@@ -2460,10 +2506,10 @@
         <v>5</v>
       </c>
       <c r="N35" s="2">
-        <v>2.0</v>
+        <v>4.72</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P35" s="2" t="s">
         <v>0</v>
@@ -2474,13 +2520,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>3</v>
@@ -2506,10 +2552,10 @@
         <v>5</v>
       </c>
       <c r="N36" s="2">
-        <v>9.67</v>
+        <v>8.92</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>0</v>
@@ -2520,13 +2566,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>3</v>
@@ -2535,27 +2581,29 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H37" s="2">
         <v>10.0</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2">
-        <v>5</v>
-      </c>
-      <c r="K37" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2">
         <v>5</v>
       </c>
       <c r="N37" s="2">
-        <v>4.23</v>
+        <v>3.68</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>0</v>
@@ -2566,13 +2614,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>3</v>
@@ -2581,27 +2629,29 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H38" s="2">
         <v>10.0</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J38" s="2">
-        <v>5</v>
-      </c>
-      <c r="K38" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2">
         <v>5</v>
       </c>
       <c r="N38" s="2">
-        <v>5.92</v>
+        <v>9.55</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>0</v>
@@ -2612,13 +2662,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>3</v>
@@ -2644,10 +2694,10 @@
         <v>5</v>
       </c>
       <c r="N39" s="2">
-        <v>7.37</v>
+        <v>2.0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>0</v>
@@ -2658,13 +2708,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>3</v>
@@ -2690,10 +2740,10 @@
         <v>5</v>
       </c>
       <c r="N40" s="2">
-        <v>4.85</v>
+        <v>9.67</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>0</v>
@@ -2704,13 +2754,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>3</v>
@@ -2736,10 +2786,10 @@
         <v>5</v>
       </c>
       <c r="N41" s="2">
-        <v>20.37</v>
+        <v>4.23</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="P41" s="2" t="s">
         <v>0</v>
@@ -2750,13 +2800,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>3</v>
@@ -2782,10 +2832,10 @@
         <v>5</v>
       </c>
       <c r="N42" s="2">
-        <v>6.92</v>
+        <v>5.92</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>0</v>
@@ -2796,13 +2846,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>3</v>
@@ -2828,10 +2878,10 @@
         <v>5</v>
       </c>
       <c r="N43" s="2">
-        <v>5.18</v>
+        <v>7.37</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P43" s="2" t="s">
         <v>0</v>
@@ -2842,13 +2892,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>3</v>
@@ -2857,31 +2907,215 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H44" s="2">
         <v>10.0</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J44" s="2">
-        <v>4</v>
-      </c>
-      <c r="K44" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2">
         <v>5</v>
       </c>
       <c r="N44" s="2">
+        <v>4.85</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="2">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="2">
+        <v>5</v>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2">
+        <v>5</v>
+      </c>
+      <c r="N45" s="2">
+        <v>20.37</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="2">
+        <v>42</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="2">
+        <v>5</v>
+      </c>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2">
+        <v>5</v>
+      </c>
+      <c r="N46" s="2">
+        <v>6.92</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="2">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="2">
+        <v>5</v>
+      </c>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2">
+        <v>5</v>
+      </c>
+      <c r="N47" s="2">
+        <v>5.18</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="2">
+        <v>44</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J48" s="2">
+        <v>4</v>
+      </c>
+      <c r="K48" s="2">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2">
+        <v>5</v>
+      </c>
+      <c r="N48" s="2">
         <v>24.78</v>
       </c>
-      <c r="O44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P44" s="2" t="s">
+      <c r="O48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="s">
         <v>0</v>
       </c>
     </row>
